--- a/stories/arbres/ATOM-TMP.MOI.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa est à la cuisine. Papa accroche un calendrier près de la fenêtre. Papa dit : il y a douze mois. Janvier, février, mars. Avril, mai, juin. Juillet, août, septembre. Octobre, novembre, décembre. Léa pose le doigt. Papa dit : octobre. L'anniversaire de Léa est en octobre. Léa répète : douze mois. Un anniversaire a un mois. Papa dessine une petite étoile sur octobre.</t>
+          <t>Léa est à la cuisine. Papa accroche un calendrier près de la fenêtre. Il y a douze mois. Janvier, février, mars. Avril, mai, juin. Juillet, août, septembre. Octobre, novembre, décembre. Léa pose le doigt. Octobre. L'anniversaire de Léa est en octobre. Léa répète : douze mois. Un anniversaire a un mois. Papa dessine une petite étoile sur octobre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa est à la cuisine. Papa accroche un calendrier près de la fenêtre.
+papa|Il y a douze mois. Janvier, février, mars. Avril, mai, juin. Juillet, août, septembre. Octobre, novembre, décembre.
+narrateur|Léa pose le doigt.
+papa|Octobre. L'anniversaire de Léa est en octobre.
+narrateur|Léa répète : douze mois. Un anniversaire a un mois. Papa dessine une petite étoile sur octobre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a un mois sur le calendrier. Pourquoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a entendu les douze mois. Son anniversaire est en octobre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le crayon. Léa touche l'étoile.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MOI.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Léa répète : douze mois. Un anniversaire a un mois. Papa dessine une petite étoile sur octobre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Léa a un mois sur le calendrier. Pourquoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Léa a entendu les douze mois. Son anniversaire est en octobre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Papa range le crayon. Léa touche l'étoile.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.MOI.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les douze mois de Léa</t>
+          <t>La page de juin</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir veut marquer le pique-nique sur le calendrier mural. Papa tourne les pages. Avril trop tôt, mai presque, juin : les fraises et la nappe. Une page colle. Amir la décolle. L'étoile est sur juin.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa est à la cuisine. Papa accroche un calendrier près de la fenêtre. Il y a douze mois. Janvier, février, mars. Avril, mai, juin. Juillet, août, septembre. Octobre, novembre, décembre. Léa pose le doigt. Octobre. L'anniversaire de Léa est en octobre. Léa répète : douze mois. Un anniversaire a un mois. Papa dessine une petite étoile sur octobre.</t>
+          <t>Le calendrier mural a une page un peu recourbée. Un coin d'encre a pâli au soleil. La cuisine sent le café froid de papa. On cherche notre pique-nique. Oui. Il faut le bon mois. Une nappe à carreaux attend sur la chaise. Pour près de la rivière. Quand le mois sera le bon. Papa accroche mieux le clou. Le calendrier se tient droit. Je tourne ? Doucement. Amir tire une page. Le papier fait un petit fsh. C'est encore avril. Les tulipes. Trop tôt pour le pique-nique. La nappe grelotterait. Amir tourne encore. Une abeille est dessinée dans un coin. Mai. Les fleurs. Presque. Les fraises ne sont pas là. En ce moment, Amir tire la page suivante. Elle colle un peu à mai. Elle ne veut pas. Un peu de patience. Amir souffle sur le bord. Il décolle le papier, tout fin. Voilà. Juin. Juin ! Les fraises. Et notre pique-nique. Une nappe à carreaux est dessinée, minuscule. Je mets une étoile ? Oui. Sur juin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léa est à la cuisine. Papa accroche un calendrier près de la fenêtre. Papa dit : il y a &lt;emphasis level="moderate"&gt;douze&lt;/emphasis&gt; mois. Janvier, février, mars. Avril, mai, juin. Juillet, août, septembre. Octobre, novembre, décembre. Léa pose le doigt. Papa dit : octobre. L'anniversaire de Léa est en octobre. Léa répète : douze mois. Un anniversaire a un mois. Papa dessine une petite étoile sur octobre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le calendrier mural a une page un peu recourbée. Un coin d'encre a pâli au soleil. La cuisine sent le café froid de papa. On cherche notre pique-nique. Oui. Il faut le bon mois. Une nappe à carreaux attend sur la chaise. Pour près de la rivière. Quand le mois sera le bon. Papa accroche mieux le clou. Le calendrier se tient droit. Je tourne ? Doucement. Amir tire une page. Le papier fait un petit fsh. C'est encore avril. Les tulipes. Trop tôt pour le pique-nique. La nappe grelotterait. Amir tourne encore. Une abeille est dessinée dans un coin. Mai. Les fleurs. Presque. Les fraises ne sont pas là. En ce moment, Amir tire la page suivante. Elle colle un peu à mai. Elle ne veut pas. Un peu de patience. Amir souffle sur le bord. Il décolle le papier, tout fin. Voilà. Juin. Juin ! Les fraises. Et notre pique-nique. Une nappe à carreaux est dessinée, minuscule. Je mets une étoile ? Oui. Sur juin.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,48 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Léa est à la cuisine. Papa accroche un calendrier près de la fenêtre.
-papa|Il y a douze mois. Janvier, février, mars. Avril, mai, juin. Juillet, août, septembre. Octobre, novembre, décembre.
-narrateur|Léa pose le doigt.
-papa|Octobre. L'anniversaire de Léa est en octobre.
-narrateur|Léa répète : douze mois. Un anniversaire a un mois. Papa dessine une petite étoile sur octobre.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le calendrier mural a une page un peu recourbée.
+narrateur|Un coin d'encre a pâli au soleil.
+narrateur|La cuisine sent le café froid de papa.
+enfant-m|On cherche notre pique-nique.
+papa|Oui.
+papa|Il faut le bon mois.
+narrateur|Une nappe à carreaux attend sur la chaise.
+enfant-m|Pour près de la rivière.
+papa|Quand le mois sera le bon.
+narrateur|Papa accroche mieux le clou.
+narrateur|Le calendrier se tient droit.
+enfant-m|Je tourne ?
+papa|Doucement.
+narrateur|Amir tire une page.
+narrateur|Le papier fait un petit fsh.
+papa|C'est encore avril.
+enfant-m|Les tulipes.
+papa|Trop tôt pour le pique-nique.
+papa|La nappe grelotterait.
+narrateur|Amir tourne encore.
+narrateur|Une abeille est dessinée dans un coin.
+papa|Mai.
+enfant-m|Les fleurs.
+papa|Presque.
+papa|Les fraises ne sont pas là.
+narrateur|En ce moment, Amir tire la page suivante.
+narrateur|Elle colle un peu à mai.
+enfant-m|Elle ne veut pas.
+papa|Un peu de patience.
+narrateur|Amir souffle sur le bord.
+narrateur|Il décolle le papier, tout fin.
+papa|Voilà.
+papa|Juin.
+enfant-m|Juin !
+papa|Les fraises.
+papa|Et notre pique-nique.
+narrateur|Une nappe à carreaux est dessinée, minuscule.
+enfant-m|Je mets une étoile ?
+papa|Oui.
+papa|Sur juin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1390,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Léa a un mois sur le calendrier. Pourquoi ?</t>
+          <t>Amir a un mois sur le calendrier. Pourquoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa a un mois sur le calendrier. Pourquoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a un mois sur le calendrier. Pourquoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1359,12 +1405,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>octobre</t>
+          <t>juin</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>octobre | un mois | anniversaire | douze mois</t>
+          <t>juin | un mois | pique-nique | fête | anniversaire</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1379,7 +1425,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il y a douze mois. Lequel est celui de Léa ?</t>
+          <t>C'est le mois du pique-nique. Quel mois cherchent-ils ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1428,7 +1474,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1500,10 +1546,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Léa a un mois sur le calendrier. Pourquoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Amir a un mois sur le calendrier.
+narrateur|Pourquoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,12 +1574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa a entendu les douze mois. Son anniversaire est en octobre.</t>
+          <t>Papa tend le crayon gras. La mine est un peu molle. Une étoile. Amir dessine cinq branches, inégales. Une branche dépasse sur le dimanche. C'est joli. C'est le mois du pique-nique. Parce que c'est juin. Oui. Un mois pour une fête. Le crayon laisse une poussière bleue. Amir souffle. Tu as trouvé la page. Merci, Amir. Elle collait. Tu l'as décollée. Avril et mai restent derrière. Juin regarde la cuisine.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léa a entendu les &lt;emphasis level="moderate"&gt;douze&lt;/emphasis&gt; mois. Son anniversaire est en octobre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa tend le crayon gras. La mine est un peu molle. Une étoile. Amir dessine cinq branches, inégales. Une branche dépasse sur le dimanche. C'est joli. C'est le mois du pique-nique. Parce que c'est juin. Oui. Un mois pour une fête. Le crayon laisse une poussière bleue. Amir souffle. Tu as trouvé la page. Merci, Amir. Elle collait. Tu l'as décollée. Avril et mai restent derrière. Juin regarde la cuisine.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1596,7 +1642,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1672,10 +1718,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa a entendu les douze mois. Son anniversaire est en octobre.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Papa tend le crayon gras.
+narrateur|La mine est un peu molle.
+enfant-m|Une étoile.
+narrateur|Amir dessine cinq branches, inégales.
+narrateur|Une branche dépasse sur le dimanche.
+papa|C'est joli.
+papa|C'est le mois du pique-nique.
+enfant-m|Parce que c'est juin.
+papa|Oui.
+papa|Un mois pour une fête.
+narrateur|Le crayon laisse une poussière bleue.
+narrateur|Amir souffle.
+papa|Tu as trouvé la page.
+papa|Merci, Amir.
+enfant-m|Elle collait.
+papa|Tu l'as décollée.
+narrateur|Avril et mai restent derrière.
+narrateur|Juin regarde la cuisine.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,12 +1762,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le crayon. Léa touche l'étoile.</t>
+          <t>Papa range le crayon dans le tiroir. Le tiroir sent le bois. On prend la nappe ? Pas encore. Le jour n'est pas venu. Amir touche l'étoile du doigt. Le papier est un peu rêche. Tu veux un verre d'eau ? Oui. L'eau claque dans le verre. Une goutte reste sur la table. Juin arrivera. Avec les fraises. Avec la nappe. Une mouche se pose sur le mot mai, derrière. Pas celle-là. Mai reste caché. Le soleil avance sur le calendrier. Il touche juste le mot juin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range le crayon. Léa touche l'étoile.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa range le crayon dans le tiroir. Le tiroir sent le bois. On prend la nappe ? Pas encore. Le jour n'est pas venu. Amir touche l'étoile du doigt. Le papier est un peu rêche. Tu veux un verre d'eau ? Oui. L'eau claque dans le verre. Une goutte reste sur la table. Juin arrivera. Avec les fraises. Avec la nappe. Une mouche se pose sur le mot mai, derrière. Pas celle-là. Mai reste caché. Le soleil avance sur le calendrier. Il touche juste le mot juin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1768,7 +1830,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1836,10 +1898,27 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le crayon. Léa touche l'étoile.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa range le crayon dans le tiroir.
+narrateur|Le tiroir sent le bois.
+enfant-m|On prend la nappe ?
+papa|Pas encore.
+papa|Le jour n'est pas venu.
+narrateur|Amir touche l'étoile du doigt.
+narrateur|Le papier est un peu rêche.
+papa|Tu veux un verre d'eau ?
+enfant-m|Oui.
+narrateur|L'eau claque dans le verre.
+narrateur|Une goutte reste sur la table.
+papa|Juin arrivera.
+enfant-m|Avec les fraises.
+papa|Avec la nappe.
+narrateur|Une mouche se pose sur le mot mai, derrière.
+enfant-m|Pas celle-là.
+papa|Mai reste caché.
+narrateur|Le soleil avance sur le calendrier.
+narrateur|Il touche juste le mot juin.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1864,12 +1943,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir recule d'un pas. L'étoile se voit de la table. Elle brille un peu. Comme le pique-nique. La page recourbée s'est calmée. Elle tient maintenant, à plat. On ne la perd plus. Non. Le café froid n'a plus d'odeur. Le mot juin reste au mur, tout net.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir recule d'un pas. L'étoile se voit de la table. Elle brille un peu. Comme le pique-nique. La page recourbée s'est calmée. Elle tient maintenant, à plat. On ne la perd plus. Non. Le café froid n'a plus d'odeur. Le mot juin reste au mur, tout net.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1925,14 +2004,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2004,10 +2083,18 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Amir recule d'un pas.
+narrateur|L'étoile se voit de la table.
+enfant-m|Elle brille un peu.
+papa|Comme le pique-nique.
+narrateur|La page recourbée s'est calmée.
+narrateur|Elle tient maintenant, à plat.
+enfant-m|On ne la perd plus.
+papa|Non.
+narrateur|Le café froid n'a plus d'odeur.
+narrateur|Le mot juin reste au mur, tout net.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2151,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MOI.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine, calendrier mural près de la fenêtre</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léa, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
